--- a/src/main/resources/assets/template/ImportBacklogWhTemplate.xlsx
+++ b/src/main/resources/assets/template/ImportBacklogWhTemplate.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backend\kvc-wh-be\src\main\resources\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6726F16E-1406-4B0C-AFCF-C452A4081300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0FA110-95FD-441B-9811-AE78A5A06142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tồn kho" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tồn kho'!$A$1:$D$1</definedName>
-  </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -28,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>BIN</t>
   </si>
@@ -41,6 +38,9 @@
   <si>
     <t>ISSUE DATE</t>
   </si>
+  <si>
+    <t>STATUS</t>
+  </si>
 </sst>
 </file>
 
@@ -49,7 +49,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -58,17 +58,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -110,17 +99,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,34 +389,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.77734375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
